--- a/slide_classification/TCGA_Results/Averaging/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -18153,7 +18153,7 @@
         <v>0</v>
       </c>
       <c r="I412" t="n">
-        <v>0.333333</v>
+        <v>0</v>
       </c>
       <c r="J412" t="n">
         <v>0</v>

--- a/slide_classification/TCGA_Results/Averaging/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Averaging/H-Optimus-1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.176405</v>
+        <v>0.025877</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.999592</v>
+        <v>0.999979</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.185103</v>
+        <v>0.040512</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.392278</v>
+        <v>0.185934</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -689,7 +689,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.203837</v>
+        <v>0.129971</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.394566</v>
+        <v>0.254287</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.221018</v>
+        <v>0.237538</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.182746</v>
+        <v>0.131865</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.18291</v>
+        <v>0.160552</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.137313</v>
+        <v>0.061851</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.99898</v>
+        <v>0.999842</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.089116</v>
+        <v>0.07267</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.447121</v>
+        <v>0.279076</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.323306</v>
+        <v>0.110754</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0.856486</v>
+        <v>0.891904</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.181291</v>
+        <v>0.213355</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.19943</v>
+        <v>0.096485</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.157892</v>
+        <v>0.07747</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.227506</v>
+        <v>0.061496</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.167727</v>
+        <v>0.112898</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.964598</v>
+        <v>0.980782</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.189612</v>
+        <v>0.063389</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.379906</v>
+        <v>0.156625</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.179288</v>
+        <v>0.238355</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.371062</v>
+        <v>0.180984</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.310907</v>
+        <v>0.213114</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1635,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.449017</v>
+        <v>0.338505</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.29477</v>
+        <v>0.258278</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.99823</v>
+        <v>0.999455</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.211628</v>
+        <v>0.092988</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.308013</v>
+        <v>0.175168</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.372017</v>
+        <v>0.338987</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.206435</v>
+        <v>0.223971</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.364392</v>
+        <v>0.281588</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.108465</v>
+        <v>0.080362</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.395758</v>
+        <v>0.215892</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.177194</v>
+        <v>0.097992</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.147175</v>
+        <v>0.129462</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.152951</v>
+        <v>0.06936199999999999</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.06965</v>
+        <v>0.047977</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.122461</v>
+        <v>0.09492</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.205798</v>
+        <v>0.120257</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0.407664</v>
+        <v>0.366543</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>0.298854</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.388707</v>
+        <v>0.563129</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.339008</v>
+        <v>0.468777</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.280739</v>
+        <v>0.107098</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.402859</v>
+        <v>0.240296</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>0.229911</v>
+        <v>0.216612</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2581,7 +2581,7 @@
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.710843</v>
+        <v>0.912843</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.117969</v>
+        <v>0.18612</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.984714</v>
+        <v>0.996884</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.311889</v>
+        <v>0.142046</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.358172</v>
+        <v>0.139664</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>0.803765</v>
+        <v>0.906509</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.175825</v>
+        <v>0.08734599999999999</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2879,10 +2879,10 @@
         <v>0.024656</v>
       </c>
       <c r="F57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.522427</v>
+        <v>0.332095</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.12278</v>
+        <v>0.126713</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.320727</v>
+        <v>0.907249</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3008,10 +3008,10 @@
         <v>0.005143</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.420196</v>
+        <v>0.564837</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.999976</v>
+        <v>0.999999</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
@@ -3094,10 +3094,10 @@
         <v>0.001547</v>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>0.338067</v>
+        <v>0.593556</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.998174</v>
+        <v>0.99973</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.396376</v>
+        <v>0.182957</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0.197046</v>
+        <v>0.46786</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.196439</v>
+        <v>0.13712</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.380902</v>
+        <v>0.197334</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3355,7 +3355,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0.338298</v>
+        <v>0.238707</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.153843</v>
+        <v>0.06712799999999999</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.316478</v>
+        <v>0.088447</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3484,7 +3484,7 @@
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.8056</v>
+        <v>0.801505</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.097833</v>
+        <v>0.070647</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.484259</v>
+        <v>0.302663</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3610,10 +3610,10 @@
         <v>0.003527</v>
       </c>
       <c r="F74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.344436</v>
+        <v>0.584647</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3653,10 +3653,10 @@
         <v>2e-06</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.41312</v>
+        <v>0.5174</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.373367</v>
+        <v>0.220999</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.988926</v>
+        <v>0.975549</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3782,10 +3782,10 @@
         <v>0.644296</v>
       </c>
       <c r="F78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G78" t="n">
-        <v>0.699465</v>
+        <v>0.470446</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.289128</v>
+        <v>0.160093</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3868,10 +3868,10 @@
         <v>0.005528</v>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.401669</v>
+        <v>0.651402</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3914,7 +3914,7 @@
         <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>0.348638</v>
+        <v>0.299528</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.917368</v>
+        <v>0.890068</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.398792</v>
+        <v>0.326615</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.114704</v>
+        <v>0.039675</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.157298</v>
+        <v>0.187892</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4126,10 +4126,10 @@
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.759674</v>
+        <v>0.244087</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.140051</v>
+        <v>0.118479</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.195602</v>
+        <v>0.07860300000000001</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.991209</v>
+        <v>0.982471</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.135103</v>
+        <v>0.028252</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.18741</v>
+        <v>0.079537</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.137314</v>
+        <v>0.081978</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.237527</v>
+        <v>0.183903</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="G94" t="n">
-        <v>0.255554</v>
+        <v>0.08099099999999999</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.198261</v>
+        <v>0.063279</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.186414</v>
+        <v>0.240454</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.187984</v>
+        <v>0.158609</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.680139</v>
+        <v>0.877207</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.933961</v>
+        <v>0.962966</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.114165</v>
+        <v>0.16968</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.998067</v>
+        <v>0.99977</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.999992</v>
+        <v>0.999997</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>1</v>
       </c>
       <c r="G103" t="n">
-        <v>0.542436</v>
+        <v>0.623312</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.284411</v>
+        <v>0.247937</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.331661</v>
+        <v>0.484209</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4986,10 +4986,10 @@
         <v>6.3e-05</v>
       </c>
       <c r="F106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.566088</v>
+        <v>0.448295</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.194787</v>
+        <v>0.169292</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.991141</v>
+        <v>0.988336</v>
       </c>
       <c r="H108" t="n">
         <v>1</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.333092</v>
+        <v>0.277811</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.994143</v>
+        <v>0.990077</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.179337</v>
+        <v>0.323324</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.317389</v>
+        <v>0.273162</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.22939</v>
+        <v>0.292846</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.148757</v>
+        <v>0.210772</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.282085</v>
+        <v>0.310072</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.351778</v>
+        <v>0.428681</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.434387</v>
+        <v>0.410812</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.22679</v>
+        <v>0.2523</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.953287</v>
+        <v>0.964717</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.253401</v>
+        <v>0.251324</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>1</v>
       </c>
       <c r="G121" t="n">
-        <v>0.620404</v>
+        <v>0.50176</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.984119</v>
+        <v>0.962432</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.9502</v>
+        <v>0.931304</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.230206</v>
+        <v>0.241764</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.204455</v>
+        <v>0.219779</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.405369</v>
+        <v>0.362142</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.17835</v>
+        <v>0.147939</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.271769</v>
+        <v>0.273787</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.943726</v>
+        <v>0.963442</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="G130" t="n">
-        <v>0.444975</v>
+        <v>0.311598</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.133396</v>
+        <v>0.229286</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.239864</v>
+        <v>0.12531</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.355216</v>
+        <v>0.346483</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>0</v>
       </c>
       <c r="G134" t="n">
-        <v>0.231709</v>
+        <v>0.131513</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.202793</v>
+        <v>0.203401</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.270123</v>
+        <v>0.360077</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.314345</v>
+        <v>0.280479</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.255638</v>
+        <v>0.244865</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6405,10 +6405,10 @@
         <v>0.008045999999999999</v>
       </c>
       <c r="F139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G139" t="n">
-        <v>0.337853</v>
+        <v>0.669552</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.193142</v>
+        <v>0.152644</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6494,7 +6494,7 @@
         <v>0</v>
       </c>
       <c r="G141" t="n">
-        <v>0.469432</v>
+        <v>0.407285</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.467044</v>
+        <v>0.314981</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.088795</v>
+        <v>0.177094</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.329713</v>
+        <v>0.47956</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.200761</v>
+        <v>0.166706</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="G146" t="n">
-        <v>0.27791</v>
+        <v>0.083716</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.366391</v>
+        <v>0.335757</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.318096</v>
+        <v>0.218494</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>1</v>
       </c>
       <c r="G149" t="n">
-        <v>0.856687</v>
+        <v>0.808595</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.233184</v>
+        <v>0.218746</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>1</v>
       </c>
       <c r="G151" t="n">
-        <v>0.65023</v>
+        <v>0.550021</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.994377</v>
+        <v>0.9992529999999999</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.354322</v>
+        <v>0.294754</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.368906</v>
+        <v>0.25922</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.320153</v>
+        <v>0.119528</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.270714</v>
+        <v>0.175539</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>0</v>
       </c>
       <c r="G157" t="n">
-        <v>0.259448</v>
+        <v>0.384297</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.438919</v>
+        <v>0.221586</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.180646</v>
+        <v>0.056483</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.192078</v>
+        <v>0.140073</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.149514</v>
+        <v>0.193875</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>1</v>
       </c>
       <c r="G162" t="n">
-        <v>0.648087</v>
+        <v>0.511385</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>1</v>
       </c>
       <c r="G163" t="n">
-        <v>0.632328</v>
+        <v>0.608412</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="G164" t="n">
-        <v>0.648844</v>
+        <v>0.67733</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.178429</v>
+        <v>0.19392</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>1</v>
       </c>
       <c r="G166" t="n">
-        <v>0.835992</v>
+        <v>0.93675</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.229055</v>
+        <v>0.260593</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7652,10 +7652,10 @@
         <v>0.028074</v>
       </c>
       <c r="F168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.451754</v>
+        <v>0.629382</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>1</v>
       </c>
       <c r="G169" t="n">
-        <v>0.528539</v>
+        <v>0.573215</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.234043</v>
+        <v>0.175909</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.390105</v>
+        <v>0.387371</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.290345</v>
+        <v>0.09374499999999999</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7870,7 +7870,7 @@
         <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.163992</v>
+        <v>0.133612</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.238569</v>
+        <v>0.138331</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.239418</v>
+        <v>0.317802</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.288008</v>
+        <v>0.2782</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.156836</v>
+        <v>0.230137</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.283066</v>
+        <v>0.222852</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.139295</v>
+        <v>0.077656</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.228696</v>
+        <v>0.154422</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.328203</v>
+        <v>0.172927</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.229404</v>
+        <v>0.226424</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.25662</v>
+        <v>0.248985</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8340,10 +8340,10 @@
         <v>2e-06</v>
       </c>
       <c r="F184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.500346</v>
+        <v>0.12303</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.250226</v>
+        <v>0.101414</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.222664</v>
+        <v>0.045128</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.191655</v>
+        <v>0.118862</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.357966</v>
+        <v>0.252545</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.18488</v>
+        <v>0.102796</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>1</v>
       </c>
       <c r="G190" t="n">
-        <v>0.893685</v>
+        <v>0.871651</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>0.547549</v>
+        <v>0.539345</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.382271</v>
+        <v>0.451628</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.476873</v>
+        <v>0.454663</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.136375</v>
+        <v>0.171432</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.384672</v>
+        <v>0.275127</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8856,10 +8856,10 @@
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.50487</v>
+        <v>0.194401</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.881481</v>
+        <v>0.609402</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.8632609999999999</v>
+        <v>0.741001</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.943528</v>
+        <v>0.886545</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>0</v>
       </c>
       <c r="G200" t="n">
-        <v>0.352547</v>
+        <v>0.248037</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.103149</v>
+        <v>0.144853</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -9117,7 +9117,7 @@
         <v>0</v>
       </c>
       <c r="G202" t="n">
-        <v>0.107029</v>
+        <v>0.13259</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -9160,7 +9160,7 @@
         <v>1</v>
       </c>
       <c r="G203" t="n">
-        <v>0.690537</v>
+        <v>0.607352</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
         <v>0</v>
       </c>
       <c r="G204" t="n">
-        <v>0.198079</v>
+        <v>0.323274</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -9246,7 +9246,7 @@
         <v>0</v>
       </c>
       <c r="G205" t="n">
-        <v>0.100246</v>
+        <v>0.210587</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -9289,7 +9289,7 @@
         <v>1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.908955</v>
+        <v>0.8625119999999999</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -9332,7 +9332,7 @@
         <v>0</v>
       </c>
       <c r="G207" t="n">
-        <v>0.270797</v>
+        <v>0.326126</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -9375,7 +9375,7 @@
         <v>0</v>
       </c>
       <c r="G208" t="n">
-        <v>0.26772</v>
+        <v>0.484064</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
         <v>0</v>
       </c>
       <c r="G209" t="n">
-        <v>0.139797</v>
+        <v>0.195229</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -9461,7 +9461,7 @@
         <v>1</v>
       </c>
       <c r="G210" t="n">
-        <v>0.991403</v>
+        <v>0.996644</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -9504,7 +9504,7 @@
         <v>0</v>
       </c>
       <c r="G211" t="n">
-        <v>0.104532</v>
+        <v>0.134004</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="G212" t="n">
-        <v>0.17601</v>
+        <v>0.208311</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -9590,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="G213" t="n">
-        <v>0.250926</v>
+        <v>0.334234</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -9633,7 +9633,7 @@
         <v>0</v>
       </c>
       <c r="G214" t="n">
-        <v>0.17064</v>
+        <v>0.190787</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -9676,7 +9676,7 @@
         <v>0</v>
       </c>
       <c r="G215" t="n">
-        <v>0.134516</v>
+        <v>0.06866800000000001</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -9716,10 +9716,10 @@
         <v>0.156954</v>
       </c>
       <c r="F216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G216" t="n">
-        <v>0.418238</v>
+        <v>0.665158</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -9762,7 +9762,7 @@
         <v>0</v>
       </c>
       <c r="G217" t="n">
-        <v>0.13404</v>
+        <v>0.17134</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -9805,7 +9805,7 @@
         <v>0</v>
       </c>
       <c r="G218" t="n">
-        <v>0.147638</v>
+        <v>0.418949</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -9848,7 +9848,7 @@
         <v>0</v>
       </c>
       <c r="G219" t="n">
-        <v>0.172958</v>
+        <v>0.172602</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -9891,7 +9891,7 @@
         <v>0</v>
       </c>
       <c r="G220" t="n">
-        <v>0.186011</v>
+        <v>0.110492</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -9934,7 +9934,7 @@
         <v>0</v>
       </c>
       <c r="G221" t="n">
-        <v>0.288381</v>
+        <v>0.266348</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -9977,7 +9977,7 @@
         <v>1</v>
       </c>
       <c r="G222" t="n">
-        <v>0.915242</v>
+        <v>0.970668</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -10020,7 +10020,7 @@
         <v>0</v>
       </c>
       <c r="G223" t="n">
-        <v>0.386146</v>
+        <v>0.456409</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -10063,7 +10063,7 @@
         <v>0</v>
       </c>
       <c r="G224" t="n">
-        <v>0.131262</v>
+        <v>0.229592</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -10106,7 +10106,7 @@
         <v>0</v>
       </c>
       <c r="G225" t="n">
-        <v>0.204064</v>
+        <v>0.413863</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -10149,7 +10149,7 @@
         <v>0</v>
       </c>
       <c r="G226" t="n">
-        <v>0.134153</v>
+        <v>0.177833</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="G227" t="n">
-        <v>0.296119</v>
+        <v>0.337226</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -10235,7 +10235,7 @@
         <v>0</v>
       </c>
       <c r="G228" t="n">
-        <v>0.143295</v>
+        <v>0.259673</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="G229" t="n">
-        <v>0.217257</v>
+        <v>0.155239</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="G230" t="n">
-        <v>0.279157</v>
+        <v>0.44755</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -10364,7 +10364,7 @@
         <v>1</v>
       </c>
       <c r="G231" t="n">
-        <v>0.803715</v>
+        <v>0.894228</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -10407,7 +10407,7 @@
         <v>1</v>
       </c>
       <c r="G232" t="n">
-        <v>0.517164</v>
+        <v>0.51542</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -10450,7 +10450,7 @@
         <v>1</v>
       </c>
       <c r="G233" t="n">
-        <v>0.999974</v>
+        <v>0.999995</v>
       </c>
       <c r="H233" t="n">
         <v>1</v>
@@ -10493,7 +10493,7 @@
         <v>0</v>
       </c>
       <c r="G234" t="n">
-        <v>0.449062</v>
+        <v>0.406855</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -10536,7 +10536,7 @@
         <v>0</v>
       </c>
       <c r="G235" t="n">
-        <v>0.364616</v>
+        <v>0.396772</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -10579,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="G236" t="n">
-        <v>0.166054</v>
+        <v>0.410678</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -10622,7 +10622,7 @@
         <v>0</v>
       </c>
       <c r="G237" t="n">
-        <v>0.123828</v>
+        <v>0.123533</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -10665,7 +10665,7 @@
         <v>0</v>
       </c>
       <c r="G238" t="n">
-        <v>0.154258</v>
+        <v>0.128904</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -10708,7 +10708,7 @@
         <v>0</v>
       </c>
       <c r="G239" t="n">
-        <v>0.100582</v>
+        <v>0.069026</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -10751,7 +10751,7 @@
         <v>0</v>
       </c>
       <c r="G240" t="n">
-        <v>0.100536</v>
+        <v>0.069331</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -10794,7 +10794,7 @@
         <v>0</v>
       </c>
       <c r="G241" t="n">
-        <v>0.206767</v>
+        <v>0.149383</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="G242" t="n">
-        <v>0.160528</v>
+        <v>0.147849</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
         <v>0</v>
       </c>
       <c r="G243" t="n">
-        <v>0.248058</v>
+        <v>0.320997</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -10920,10 +10920,10 @@
         <v>0.001677</v>
       </c>
       <c r="F244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G244" t="n">
-        <v>0.334657</v>
+        <v>0.640701</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -10966,7 +10966,7 @@
         <v>1</v>
       </c>
       <c r="G245" t="n">
-        <v>0.839238</v>
+        <v>0.564137</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -11009,7 +11009,7 @@
         <v>1</v>
       </c>
       <c r="G246" t="n">
-        <v>0.996025</v>
+        <v>0.998377</v>
       </c>
       <c r="H246" t="n">
         <v>1</v>
@@ -11052,7 +11052,7 @@
         <v>1</v>
       </c>
       <c r="G247" t="n">
-        <v>0.991329</v>
+        <v>0.998271</v>
       </c>
       <c r="H247" t="n">
         <v>1</v>
@@ -11095,7 +11095,7 @@
         <v>1</v>
       </c>
       <c r="G248" t="n">
-        <v>0.829832</v>
+        <v>0.804454</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -11138,7 +11138,7 @@
         <v>1</v>
       </c>
       <c r="G249" t="n">
-        <v>0.999292</v>
+        <v>0.999851</v>
       </c>
       <c r="H249" t="n">
         <v>1</v>
@@ -11181,7 +11181,7 @@
         <v>0</v>
       </c>
       <c r="G250" t="n">
-        <v>0.211231</v>
+        <v>0.187678</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -11224,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="G251" t="n">
-        <v>0.146367</v>
+        <v>0.369348</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -11267,7 +11267,7 @@
         <v>1</v>
       </c>
       <c r="G252" t="n">
-        <v>0.852827</v>
+        <v>0.92855</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -11310,7 +11310,7 @@
         <v>0</v>
       </c>
       <c r="G253" t="n">
-        <v>0.2429</v>
+        <v>0.171993</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -11353,7 +11353,7 @@
         <v>0</v>
       </c>
       <c r="G254" t="n">
-        <v>0.412769</v>
+        <v>0.223899</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -11393,10 +11393,10 @@
         <v>0.00249</v>
       </c>
       <c r="F255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G255" t="n">
-        <v>0.64094</v>
+        <v>0.477345</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -11439,7 +11439,7 @@
         <v>1</v>
       </c>
       <c r="G256" t="n">
-        <v>0.977708</v>
+        <v>0.993368</v>
       </c>
       <c r="H256" t="n">
         <v>1</v>
@@ -11482,7 +11482,7 @@
         <v>1</v>
       </c>
       <c r="G257" t="n">
-        <v>0.821271</v>
+        <v>0.94394</v>
       </c>
       <c r="H257" t="n">
         <v>1</v>
@@ -11525,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="G258" t="n">
-        <v>0.999201</v>
+        <v>0.999723</v>
       </c>
       <c r="H258" t="n">
         <v>1</v>
@@ -11568,7 +11568,7 @@
         <v>1</v>
       </c>
       <c r="G259" t="n">
-        <v>0.743905</v>
+        <v>0.735845</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -11611,7 +11611,7 @@
         <v>0</v>
       </c>
       <c r="G260" t="n">
-        <v>0.176797</v>
+        <v>0.134278</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="G261" t="n">
-        <v>0.450873</v>
+        <v>0.322481</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -11697,7 +11697,7 @@
         <v>1</v>
       </c>
       <c r="G262" t="n">
-        <v>0.732511</v>
+        <v>0.701877</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -11740,7 +11740,7 @@
         <v>0</v>
       </c>
       <c r="G263" t="n">
-        <v>0.23341</v>
+        <v>0.132847</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -11783,7 +11783,7 @@
         <v>1</v>
       </c>
       <c r="G264" t="n">
-        <v>0.9710029999999999</v>
+        <v>0.988998</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -11826,7 +11826,7 @@
         <v>0</v>
       </c>
       <c r="G265" t="n">
-        <v>0.294026</v>
+        <v>0.284221</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -11869,7 +11869,7 @@
         <v>0</v>
       </c>
       <c r="G266" t="n">
-        <v>0.171206</v>
+        <v>0.086216</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="G267" t="n">
-        <v>0.935075</v>
+        <v>0.944096</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -11955,7 +11955,7 @@
         <v>1</v>
       </c>
       <c r="G268" t="n">
-        <v>0.8624810000000001</v>
+        <v>0.92872</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -11998,7 +11998,7 @@
         <v>0</v>
       </c>
       <c r="G269" t="n">
-        <v>0.247097</v>
+        <v>0.200087</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -12041,7 +12041,7 @@
         <v>0</v>
       </c>
       <c r="G270" t="n">
-        <v>0.238163</v>
+        <v>0.286923</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>0</v>
       </c>
       <c r="G271" t="n">
-        <v>0.153488</v>
+        <v>0.160767</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -12127,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="G272" t="n">
-        <v>0.38598</v>
+        <v>0.313893</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>1</v>
       </c>
       <c r="G273" t="n">
-        <v>0.663006</v>
+        <v>0.6965209999999999</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -12213,7 +12213,7 @@
         <v>1</v>
       </c>
       <c r="G274" t="n">
-        <v>0.995719</v>
+        <v>0.99318</v>
       </c>
       <c r="H274" t="n">
         <v>0</v>
@@ -12256,7 +12256,7 @@
         <v>0</v>
       </c>
       <c r="G275" t="n">
-        <v>0.470462</v>
+        <v>0.210083</v>
       </c>
       <c r="H275" t="n">
         <v>0</v>
@@ -12299,7 +12299,7 @@
         <v>1</v>
       </c>
       <c r="G276" t="n">
-        <v>0.786828</v>
+        <v>0.833716</v>
       </c>
       <c r="H276" t="n">
         <v>0</v>
@@ -12339,10 +12339,10 @@
         <v>0.000291</v>
       </c>
       <c r="F277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G277" t="n">
-        <v>0.25749</v>
+        <v>0.506234</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -12385,7 +12385,7 @@
         <v>1</v>
       </c>
       <c r="G278" t="n">
-        <v>0.526817</v>
+        <v>0.502726</v>
       </c>
       <c r="H278" t="n">
         <v>0</v>
@@ -12428,7 +12428,7 @@
         <v>0</v>
       </c>
       <c r="G279" t="n">
-        <v>0.262502</v>
+        <v>0.258731</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -12471,7 +12471,7 @@
         <v>0</v>
       </c>
       <c r="G280" t="n">
-        <v>0.174497</v>
+        <v>0.230468</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -12514,7 +12514,7 @@
         <v>0</v>
       </c>
       <c r="G281" t="n">
-        <v>0.186385</v>
+        <v>0.143739</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="G282" t="n">
-        <v>0.136406</v>
+        <v>0.151181</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -12600,7 +12600,7 @@
         <v>0</v>
       </c>
       <c r="G283" t="n">
-        <v>0.160284</v>
+        <v>0.132884</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -12643,7 +12643,7 @@
         <v>0</v>
       </c>
       <c r="G284" t="n">
-        <v>0.222987</v>
+        <v>0.308734</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -12683,10 +12683,10 @@
         <v>0.000166</v>
       </c>
       <c r="F285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G285" t="n">
-        <v>0.570919</v>
+        <v>0.429373</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -12729,7 +12729,7 @@
         <v>1</v>
       </c>
       <c r="G286" t="n">
-        <v>0.613156</v>
+        <v>0.6825599999999999</v>
       </c>
       <c r="H286" t="n">
         <v>0</v>
@@ -12772,7 +12772,7 @@
         <v>1</v>
       </c>
       <c r="G287" t="n">
-        <v>0.851731</v>
+        <v>0.795673</v>
       </c>
       <c r="H287" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="G288" t="n">
-        <v>0.402892</v>
+        <v>0.191742</v>
       </c>
       <c r="H288" t="n">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>0</v>
       </c>
       <c r="G289" t="n">
-        <v>0.318833</v>
+        <v>0.254186</v>
       </c>
       <c r="H289" t="n">
         <v>0</v>
@@ -12901,7 +12901,7 @@
         <v>0</v>
       </c>
       <c r="G290" t="n">
-        <v>0.439289</v>
+        <v>0.260533</v>
       </c>
       <c r="H290" t="n">
         <v>0</v>
@@ -12944,7 +12944,7 @@
         <v>0</v>
       </c>
       <c r="G291" t="n">
-        <v>0.312142</v>
+        <v>0.341038</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -12987,7 +12987,7 @@
         <v>1</v>
       </c>
       <c r="G292" t="n">
-        <v>0.549336</v>
+        <v>0.530043</v>
       </c>
       <c r="H292" t="n">
         <v>0</v>
@@ -13030,7 +13030,7 @@
         <v>0</v>
       </c>
       <c r="G293" t="n">
-        <v>0.306579</v>
+        <v>0.324203</v>
       </c>
       <c r="H293" t="n">
         <v>0</v>
@@ -13073,7 +13073,7 @@
         <v>0</v>
       </c>
       <c r="G294" t="n">
-        <v>0.102639</v>
+        <v>0.200989</v>
       </c>
       <c r="H294" t="n">
         <v>0</v>
@@ -13116,7 +13116,7 @@
         <v>0</v>
       </c>
       <c r="G295" t="n">
-        <v>0.189425</v>
+        <v>0.154471</v>
       </c>
       <c r="H295" t="n">
         <v>0</v>
@@ -13159,7 +13159,7 @@
         <v>1</v>
       </c>
       <c r="G296" t="n">
-        <v>0.999973</v>
+        <v>0.99993</v>
       </c>
       <c r="H296" t="n">
         <v>1</v>
@@ -13202,7 +13202,7 @@
         <v>1</v>
       </c>
       <c r="G297" t="n">
-        <v>0.659842</v>
+        <v>0.699061</v>
       </c>
       <c r="H297" t="n">
         <v>0</v>
@@ -13245,7 +13245,7 @@
         <v>0</v>
       </c>
       <c r="G298" t="n">
-        <v>0.306221</v>
+        <v>0.275152</v>
       </c>
       <c r="H298" t="n">
         <v>0</v>
@@ -13288,7 +13288,7 @@
         <v>0</v>
       </c>
       <c r="G299" t="n">
-        <v>0.404586</v>
+        <v>0.349653</v>
       </c>
       <c r="H299" t="n">
         <v>0</v>
@@ -13331,7 +13331,7 @@
         <v>0</v>
       </c>
       <c r="G300" t="n">
-        <v>0.464884</v>
+        <v>0.278025</v>
       </c>
       <c r="H300" t="n">
         <v>0</v>
@@ -13374,7 +13374,7 @@
         <v>0</v>
       </c>
       <c r="G301" t="n">
-        <v>0.16251</v>
+        <v>0.14513</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -13417,7 +13417,7 @@
         <v>0</v>
       </c>
       <c r="G302" t="n">
-        <v>0.420555</v>
+        <v>0.490991</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -13460,7 +13460,7 @@
         <v>1</v>
       </c>
       <c r="G303" t="n">
-        <v>0.833057</v>
+        <v>0.947739</v>
       </c>
       <c r="H303" t="n">
         <v>1</v>
@@ -13503,7 +13503,7 @@
         <v>1</v>
       </c>
       <c r="G304" t="n">
-        <v>0.798945</v>
+        <v>0.900259</v>
       </c>
       <c r="H304" t="n">
         <v>1</v>
@@ -13546,7 +13546,7 @@
         <v>0</v>
       </c>
       <c r="G305" t="n">
-        <v>0.129249</v>
+        <v>0.207249</v>
       </c>
       <c r="H305" t="n">
         <v>0</v>
@@ -13589,7 +13589,7 @@
         <v>0</v>
       </c>
       <c r="G306" t="n">
-        <v>0.423237</v>
+        <v>0.40493</v>
       </c>
       <c r="H306" t="n">
         <v>0</v>
@@ -13632,7 +13632,7 @@
         <v>0</v>
       </c>
       <c r="G307" t="n">
-        <v>0.216096</v>
+        <v>0.242073</v>
       </c>
       <c r="H307" t="n">
         <v>0</v>
@@ -13675,7 +13675,7 @@
         <v>0</v>
       </c>
       <c r="G308" t="n">
-        <v>0.174948</v>
+        <v>0.135615</v>
       </c>
       <c r="H308" t="n">
         <v>0</v>
@@ -13718,7 +13718,7 @@
         <v>1</v>
       </c>
       <c r="G309" t="n">
-        <v>0.660366</v>
+        <v>0.7281069999999999</v>
       </c>
       <c r="H309" t="n">
         <v>1</v>
@@ -13761,7 +13761,7 @@
         <v>0</v>
       </c>
       <c r="G310" t="n">
-        <v>0.05735</v>
+        <v>0.075673</v>
       </c>
       <c r="H310" t="n">
         <v>0</v>
@@ -13804,7 +13804,7 @@
         <v>0</v>
       </c>
       <c r="G311" t="n">
-        <v>0.136633</v>
+        <v>0.206373</v>
       </c>
       <c r="H311" t="n">
         <v>0</v>
@@ -13847,7 +13847,7 @@
         <v>0</v>
       </c>
       <c r="G312" t="n">
-        <v>0.161766</v>
+        <v>0.153235</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -13890,7 +13890,7 @@
         <v>0</v>
       </c>
       <c r="G313" t="n">
-        <v>0.2316</v>
+        <v>0.396568</v>
       </c>
       <c r="H313" t="n">
         <v>0</v>
@@ -13933,7 +13933,7 @@
         <v>0</v>
       </c>
       <c r="G314" t="n">
-        <v>0.13849</v>
+        <v>0.230073</v>
       </c>
       <c r="H314" t="n">
         <v>0</v>
@@ -13976,7 +13976,7 @@
         <v>0</v>
       </c>
       <c r="G315" t="n">
-        <v>0.25522</v>
+        <v>0.117907</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="G316" t="n">
-        <v>0.4432</v>
+        <v>0.172172</v>
       </c>
       <c r="H316" t="n">
         <v>0</v>
@@ -14062,7 +14062,7 @@
         <v>0</v>
       </c>
       <c r="G317" t="n">
-        <v>0.177572</v>
+        <v>0.079766</v>
       </c>
       <c r="H317" t="n">
         <v>0</v>
@@ -14105,7 +14105,7 @@
         <v>1</v>
       </c>
       <c r="G318" t="n">
-        <v>0.659801</v>
+        <v>0.515795</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -14145,10 +14145,10 @@
         <v>5.7e-05</v>
       </c>
       <c r="F319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G319" t="n">
-        <v>0.536511</v>
+        <v>0.401019</v>
       </c>
       <c r="H319" t="n">
         <v>0</v>
@@ -14191,7 +14191,7 @@
         <v>1</v>
       </c>
       <c r="G320" t="n">
-        <v>0.996949</v>
+        <v>0.997603</v>
       </c>
       <c r="H320" t="n">
         <v>1</v>
@@ -14234,7 +14234,7 @@
         <v>0</v>
       </c>
       <c r="G321" t="n">
-        <v>0.239417</v>
+        <v>0.144566</v>
       </c>
       <c r="H321" t="n">
         <v>0</v>
@@ -14277,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="G322" t="n">
-        <v>0.101265</v>
+        <v>0.220499</v>
       </c>
       <c r="H322" t="n">
         <v>0</v>
@@ -14320,7 +14320,7 @@
         <v>0</v>
       </c>
       <c r="G323" t="n">
-        <v>0.270431</v>
+        <v>0.133927</v>
       </c>
       <c r="H323" t="n">
         <v>0</v>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="G324" t="n">
-        <v>0.313734</v>
+        <v>0.323656</v>
       </c>
       <c r="H324" t="n">
         <v>0</v>
@@ -14406,7 +14406,7 @@
         <v>0</v>
       </c>
       <c r="G325" t="n">
-        <v>0.252214</v>
+        <v>0.09327100000000001</v>
       </c>
       <c r="H325" t="n">
         <v>0</v>
@@ -14449,7 +14449,7 @@
         <v>0</v>
       </c>
       <c r="G326" t="n">
-        <v>0.391136</v>
+        <v>0.227573</v>
       </c>
       <c r="H326" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>0</v>
       </c>
       <c r="G327" t="n">
-        <v>0.485814</v>
+        <v>0.348695</v>
       </c>
       <c r="H327" t="n">
         <v>0</v>
@@ -14535,7 +14535,7 @@
         <v>1</v>
       </c>
       <c r="G328" t="n">
-        <v>0.923116</v>
+        <v>0.98449</v>
       </c>
       <c r="H328" t="n">
         <v>1</v>
@@ -14578,7 +14578,7 @@
         <v>0</v>
       </c>
       <c r="G329" t="n">
-        <v>0.460178</v>
+        <v>0.235571</v>
       </c>
       <c r="H329" t="n">
         <v>0</v>
@@ -14621,7 +14621,7 @@
         <v>0</v>
       </c>
       <c r="G330" t="n">
-        <v>0.259482</v>
+        <v>0.171658</v>
       </c>
       <c r="H330" t="n">
         <v>0</v>
@@ -14664,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="G331" t="n">
-        <v>0.9910870000000001</v>
+        <v>0.991959</v>
       </c>
       <c r="H331" t="n">
         <v>1</v>
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="G332" t="n">
-        <v>0.18497</v>
+        <v>0.07635</v>
       </c>
       <c r="H332" t="n">
         <v>0</v>
@@ -14750,7 +14750,7 @@
         <v>1</v>
       </c>
       <c r="G333" t="n">
-        <v>0.997992</v>
+        <v>0.999739</v>
       </c>
       <c r="H333" t="n">
         <v>1</v>
@@ -14793,7 +14793,7 @@
         <v>0</v>
       </c>
       <c r="G334" t="n">
-        <v>0.336015</v>
+        <v>0.231912</v>
       </c>
       <c r="H334" t="n">
         <v>0</v>
@@ -14836,7 +14836,7 @@
         <v>0</v>
       </c>
       <c r="G335" t="n">
-        <v>0.383146</v>
+        <v>0.169007</v>
       </c>
       <c r="H335" t="n">
         <v>0</v>
@@ -14876,10 +14876,10 @@
         <v>0.054323</v>
       </c>
       <c r="F336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G336" t="n">
-        <v>0.718516</v>
+        <v>0.401471</v>
       </c>
       <c r="H336" t="n">
         <v>0</v>
@@ -14922,7 +14922,7 @@
         <v>0</v>
       </c>
       <c r="G337" t="n">
-        <v>0.148306</v>
+        <v>0.049618</v>
       </c>
       <c r="H337" t="n">
         <v>0</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
       <c r="G338" t="n">
-        <v>0.272448</v>
+        <v>0.095305</v>
       </c>
       <c r="H338" t="n">
         <v>0</v>
@@ -15008,7 +15008,7 @@
         <v>0</v>
       </c>
       <c r="G339" t="n">
-        <v>0.137259</v>
+        <v>0.118383</v>
       </c>
       <c r="H339" t="n">
         <v>0</v>
@@ -15051,7 +15051,7 @@
         <v>0</v>
       </c>
       <c r="G340" t="n">
-        <v>0.440157</v>
+        <v>0.292426</v>
       </c>
       <c r="H340" t="n">
         <v>0</v>
@@ -15094,7 +15094,7 @@
         <v>0</v>
       </c>
       <c r="G341" t="n">
-        <v>0.414928</v>
+        <v>0.400975</v>
       </c>
       <c r="H341" t="n">
         <v>0</v>
@@ -15137,7 +15137,7 @@
         <v>0</v>
       </c>
       <c r="G342" t="n">
-        <v>0.143333</v>
+        <v>0.0564</v>
       </c>
       <c r="H342" t="n">
         <v>0</v>
@@ -15180,7 +15180,7 @@
         <v>0</v>
       </c>
       <c r="G343" t="n">
-        <v>0.108114</v>
+        <v>0.09482599999999999</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -15223,7 +15223,7 @@
         <v>0</v>
       </c>
       <c r="G344" t="n">
-        <v>0.115556</v>
+        <v>0.076225</v>
       </c>
       <c r="H344" t="n">
         <v>0</v>
@@ -15263,10 +15263,10 @@
         <v>0.011677</v>
       </c>
       <c r="F345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G345" t="n">
-        <v>0.477111</v>
+        <v>0.517269</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -15309,7 +15309,7 @@
         <v>0</v>
       </c>
       <c r="G346" t="n">
-        <v>0.481785</v>
+        <v>0.317121</v>
       </c>
       <c r="H346" t="n">
         <v>0</v>
@@ -15352,7 +15352,7 @@
         <v>0</v>
       </c>
       <c r="G347" t="n">
-        <v>0.469401</v>
+        <v>0.314288</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -15395,7 +15395,7 @@
         <v>0</v>
       </c>
       <c r="G348" t="n">
-        <v>0.21515</v>
+        <v>0.355273</v>
       </c>
       <c r="H348" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="G349" t="n">
-        <v>0.42202</v>
+        <v>0.496455</v>
       </c>
       <c r="H349" t="n">
         <v>0</v>
@@ -15481,7 +15481,7 @@
         <v>1</v>
       </c>
       <c r="G350" t="n">
-        <v>0.799998</v>
+        <v>0.839488</v>
       </c>
       <c r="H350" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="G351" t="n">
-        <v>0.366869</v>
+        <v>0.382275</v>
       </c>
       <c r="H351" t="n">
         <v>0</v>
@@ -15567,7 +15567,7 @@
         <v>0</v>
       </c>
       <c r="G352" t="n">
-        <v>0.258668</v>
+        <v>0.316154</v>
       </c>
       <c r="H352" t="n">
         <v>0</v>
@@ -15610,7 +15610,7 @@
         <v>0</v>
       </c>
       <c r="G353" t="n">
-        <v>0.104539</v>
+        <v>0.06790499999999999</v>
       </c>
       <c r="H353" t="n">
         <v>0</v>
@@ -15653,7 +15653,7 @@
         <v>0</v>
       </c>
       <c r="G354" t="n">
-        <v>0.185626</v>
+        <v>0.184339</v>
       </c>
       <c r="H354" t="n">
         <v>0</v>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
       <c r="G355" t="n">
-        <v>0.160505</v>
+        <v>0.08573799999999999</v>
       </c>
       <c r="H355" t="n">
         <v>0</v>
@@ -15739,7 +15739,7 @@
         <v>0</v>
       </c>
       <c r="G356" t="n">
-        <v>0.064289</v>
+        <v>0.038043</v>
       </c>
       <c r="H356" t="n">
         <v>0</v>
@@ -15782,7 +15782,7 @@
         <v>0</v>
       </c>
       <c r="G357" t="n">
-        <v>0.146792</v>
+        <v>0.162163</v>
       </c>
       <c r="H357" t="n">
         <v>0</v>
@@ -15825,7 +15825,7 @@
         <v>1</v>
       </c>
       <c r="G358" t="n">
-        <v>0.609066</v>
+        <v>0.701213</v>
       </c>
       <c r="H358" t="n">
         <v>0</v>
@@ -15868,7 +15868,7 @@
         <v>0</v>
       </c>
       <c r="G359" t="n">
-        <v>0.13744</v>
+        <v>0.08039</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -15908,10 +15908,10 @@
         <v>0.001863</v>
       </c>
       <c r="F360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G360" t="n">
-        <v>0.469995</v>
+        <v>0.573902</v>
       </c>
       <c r="H360" t="n">
         <v>0</v>
@@ -15954,7 +15954,7 @@
         <v>0</v>
       </c>
       <c r="G361" t="n">
-        <v>0.349642</v>
+        <v>0.19255</v>
       </c>
       <c r="H361" t="n">
         <v>0</v>
@@ -15997,7 +15997,7 @@
         <v>1</v>
       </c>
       <c r="G362" t="n">
-        <v>0.962076</v>
+        <v>0.864358</v>
       </c>
       <c r="H362" t="n">
         <v>0</v>
@@ -16040,7 +16040,7 @@
         <v>0</v>
       </c>
       <c r="G363" t="n">
-        <v>0.268481</v>
+        <v>0.134301</v>
       </c>
       <c r="H363" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>1</v>
       </c>
       <c r="G364" t="n">
-        <v>0.948936</v>
+        <v>0.822406</v>
       </c>
       <c r="H364" t="n">
         <v>1</v>
@@ -16126,7 +16126,7 @@
         <v>0</v>
       </c>
       <c r="G365" t="n">
-        <v>0.237134</v>
+        <v>0.2245</v>
       </c>
       <c r="H365" t="n">
         <v>0</v>
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="G366" t="n">
-        <v>0.342109</v>
+        <v>0.287587</v>
       </c>
       <c r="H366" t="n">
         <v>0</v>
@@ -16212,7 +16212,7 @@
         <v>1</v>
       </c>
       <c r="G367" t="n">
-        <v>0.568727</v>
+        <v>0.65748</v>
       </c>
       <c r="H367" t="n">
         <v>0</v>
@@ -16255,7 +16255,7 @@
         <v>0</v>
       </c>
       <c r="G368" t="n">
-        <v>0.268966</v>
+        <v>0.315254</v>
       </c>
       <c r="H368" t="n">
         <v>0</v>
@@ -16298,7 +16298,7 @@
         <v>0</v>
       </c>
       <c r="G369" t="n">
-        <v>0.228391</v>
+        <v>0.203708</v>
       </c>
       <c r="H369" t="n">
         <v>0</v>
@@ -16341,7 +16341,7 @@
         <v>0</v>
       </c>
       <c r="G370" t="n">
-        <v>0.240222</v>
+        <v>0.28126</v>
       </c>
       <c r="H370" t="n">
         <v>0</v>
@@ -16384,7 +16384,7 @@
         <v>0</v>
       </c>
       <c r="G371" t="n">
-        <v>0.334755</v>
+        <v>0.323846</v>
       </c>
       <c r="H371" t="n">
         <v>0</v>
@@ -16427,7 +16427,7 @@
         <v>0</v>
       </c>
       <c r="G372" t="n">
-        <v>0.27096</v>
+        <v>0.182398</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -16470,7 +16470,7 @@
         <v>0</v>
       </c>
       <c r="G373" t="n">
-        <v>0.167162</v>
+        <v>0.274305</v>
       </c>
       <c r="H373" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
         <v>1</v>
       </c>
       <c r="G374" t="n">
-        <v>0.5851460000000001</v>
+        <v>0.605121</v>
       </c>
       <c r="H374" t="n">
         <v>0</v>
@@ -16556,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="G375" t="n">
-        <v>0.289635</v>
+        <v>0.197434</v>
       </c>
       <c r="H375" t="n">
         <v>0</v>
@@ -16599,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="G376" t="n">
-        <v>0.452376</v>
+        <v>0.396258</v>
       </c>
       <c r="H376" t="n">
         <v>0</v>
@@ -16642,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="G377" t="n">
-        <v>0.262229</v>
+        <v>0.147234</v>
       </c>
       <c r="H377" t="n">
         <v>0</v>
@@ -16685,7 +16685,7 @@
         <v>0</v>
       </c>
       <c r="G378" t="n">
-        <v>0.381619</v>
+        <v>0.14998</v>
       </c>
       <c r="H378" t="n">
         <v>0</v>
@@ -16728,7 +16728,7 @@
         <v>0</v>
       </c>
       <c r="G379" t="n">
-        <v>0.288211</v>
+        <v>0.173892</v>
       </c>
       <c r="H379" t="n">
         <v>0</v>
@@ -16771,7 +16771,7 @@
         <v>1</v>
       </c>
       <c r="G380" t="n">
-        <v>0.53204</v>
+        <v>0.560822</v>
       </c>
       <c r="H380" t="n">
         <v>0</v>
@@ -16814,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="G381" t="n">
-        <v>0.202168</v>
+        <v>0.379683</v>
       </c>
       <c r="H381" t="n">
         <v>0</v>
@@ -16857,7 +16857,7 @@
         <v>0</v>
       </c>
       <c r="G382" t="n">
-        <v>0.429653</v>
+        <v>0.429584</v>
       </c>
       <c r="H382" t="n">
         <v>0</v>
@@ -16900,7 +16900,7 @@
         <v>0</v>
       </c>
       <c r="G383" t="n">
-        <v>0.135688</v>
+        <v>0.06537900000000001</v>
       </c>
       <c r="H383" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         <v>0</v>
       </c>
       <c r="G384" t="n">
-        <v>0.231065</v>
+        <v>0.140395</v>
       </c>
       <c r="H384" t="n">
         <v>0</v>
@@ -16986,7 +16986,7 @@
         <v>0</v>
       </c>
       <c r="G385" t="n">
-        <v>0.271796</v>
+        <v>0.084906</v>
       </c>
       <c r="H385" t="n">
         <v>0</v>
@@ -17029,7 +17029,7 @@
         <v>0</v>
       </c>
       <c r="G386" t="n">
-        <v>0.268472</v>
+        <v>0.08207200000000001</v>
       </c>
       <c r="H386" t="n">
         <v>0</v>
@@ -17069,10 +17069,10 @@
         <v>0.018744</v>
       </c>
       <c r="F387" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G387" t="n">
-        <v>0.5106849999999999</v>
+        <v>0.370832</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -17115,7 +17115,7 @@
         <v>0</v>
       </c>
       <c r="G388" t="n">
-        <v>0.315324</v>
+        <v>0.210532</v>
       </c>
       <c r="H388" t="n">
         <v>0</v>
@@ -17158,7 +17158,7 @@
         <v>0</v>
       </c>
       <c r="G389" t="n">
-        <v>0.321908</v>
+        <v>0.221984</v>
       </c>
       <c r="H389" t="n">
         <v>0</v>
@@ -17201,7 +17201,7 @@
         <v>0</v>
       </c>
       <c r="G390" t="n">
-        <v>0.456253</v>
+        <v>0.446373</v>
       </c>
       <c r="H390" t="n">
         <v>0</v>
@@ -17244,7 +17244,7 @@
         <v>0</v>
       </c>
       <c r="G391" t="n">
-        <v>0.219055</v>
+        <v>0.12093</v>
       </c>
       <c r="H391" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>1</v>
       </c>
       <c r="G392" t="n">
-        <v>0.515832</v>
+        <v>0.592375</v>
       </c>
       <c r="H392" t="n">
         <v>0</v>
@@ -17330,7 +17330,7 @@
         <v>1</v>
       </c>
       <c r="G393" t="n">
-        <v>0.720579</v>
+        <v>0.688981</v>
       </c>
       <c r="H393" t="n">
         <v>1</v>
@@ -17373,7 +17373,7 @@
         <v>0</v>
       </c>
       <c r="G394" t="n">
-        <v>0.159994</v>
+        <v>0.124475</v>
       </c>
       <c r="H394" t="n">
         <v>0</v>
@@ -17416,7 +17416,7 @@
         <v>1</v>
       </c>
       <c r="G395" t="n">
-        <v>0.681137</v>
+        <v>0.69098</v>
       </c>
       <c r="H395" t="n">
         <v>0</v>
@@ -17459,7 +17459,7 @@
         <v>0</v>
       </c>
       <c r="G396" t="n">
-        <v>0.301013</v>
+        <v>0.316475</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -17502,7 +17502,7 @@
         <v>1</v>
       </c>
       <c r="G397" t="n">
-        <v>0.8310070000000001</v>
+        <v>0.6088</v>
       </c>
       <c r="H397" t="n">
         <v>0</v>
@@ -17545,7 +17545,7 @@
         <v>0</v>
       </c>
       <c r="G398" t="n">
-        <v>0.375046</v>
+        <v>0.303721</v>
       </c>
       <c r="H398" t="n">
         <v>0</v>
@@ -17588,7 +17588,7 @@
         <v>0</v>
       </c>
       <c r="G399" t="n">
-        <v>0.292521</v>
+        <v>0.227394</v>
       </c>
       <c r="H399" t="n">
         <v>0</v>
@@ -17631,7 +17631,7 @@
         <v>0</v>
       </c>
       <c r="G400" t="n">
-        <v>0.446254</v>
+        <v>0.285158</v>
       </c>
       <c r="H400" t="n">
         <v>0</v>
@@ -17674,7 +17674,7 @@
         <v>0</v>
       </c>
       <c r="G401" t="n">
-        <v>0.407535</v>
+        <v>0.349559</v>
       </c>
       <c r="H401" t="n">
         <v>0</v>
@@ -17717,7 +17717,7 @@
         <v>0</v>
       </c>
       <c r="G402" t="n">
-        <v>0.301974</v>
+        <v>0.175787</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -17760,7 +17760,7 @@
         <v>1</v>
       </c>
       <c r="G403" t="n">
-        <v>0.9577909999999999</v>
+        <v>0.974139</v>
       </c>
       <c r="H403" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>0</v>
       </c>
       <c r="G404" t="n">
-        <v>0.281142</v>
+        <v>0.141828</v>
       </c>
       <c r="H404" t="n">
         <v>0</v>
@@ -17846,7 +17846,7 @@
         <v>0</v>
       </c>
       <c r="G405" t="n">
-        <v>0.165772</v>
+        <v>0.102934</v>
       </c>
       <c r="H405" t="n">
         <v>0</v>
@@ -17889,7 +17889,7 @@
         <v>0</v>
       </c>
       <c r="G406" t="n">
-        <v>0.366989</v>
+        <v>0.148093</v>
       </c>
       <c r="H406" t="n">
         <v>0</v>
@@ -17932,7 +17932,7 @@
         <v>0</v>
       </c>
       <c r="G407" t="n">
-        <v>0.363306</v>
+        <v>0.313752</v>
       </c>
       <c r="H407" t="n">
         <v>0</v>
@@ -17975,7 +17975,7 @@
         <v>1</v>
       </c>
       <c r="G408" t="n">
-        <v>0.875076</v>
+        <v>0.639823</v>
       </c>
       <c r="H408" t="n">
         <v>0</v>
@@ -18018,7 +18018,7 @@
         <v>1</v>
       </c>
       <c r="G409" t="n">
-        <v>0.737428</v>
+        <v>0.619244</v>
       </c>
       <c r="H409" t="n">
         <v>0</v>
@@ -18061,7 +18061,7 @@
         <v>0</v>
       </c>
       <c r="G410" t="n">
-        <v>0.180486</v>
+        <v>0.153048</v>
       </c>
       <c r="H410" t="n">
         <v>0</v>
@@ -18104,7 +18104,7 @@
         <v>1</v>
       </c>
       <c r="G411" t="n">
-        <v>0.650201</v>
+        <v>0.86289</v>
       </c>
       <c r="H411" t="n">
         <v>0</v>
@@ -18144,10 +18144,10 @@
         <v>0.138067</v>
       </c>
       <c r="F412" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G412" t="n">
-        <v>0.348358</v>
+        <v>0.523452</v>
       </c>
       <c r="H412" t="n">
         <v>0</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
       <c r="G413" t="n">
-        <v>0.246985</v>
+        <v>0.13568</v>
       </c>
       <c r="H413" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>1</v>
       </c>
       <c r="G414" t="n">
-        <v>0.73131</v>
+        <v>0.8223200000000001</v>
       </c>
       <c r="H414" t="n">
         <v>1</v>
